--- a/tamu_data/evals/reports/eval_curated20_v2_cap4_20260521_20260521_200401.xlsx
+++ b/tamu_data/evals/reports/eval_curated20_v2_cap4_20260521_20260521_200401.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Definitions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per-Query'!$A$1:$AF$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per-Query'!$A$1:$AG$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,16 @@
       </c>
       <c r="B20" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mean chunk tokens (backfilled)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1089.5</v>
       </c>
     </row>
   </sheetData>
@@ -673,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -773,100 +783,105 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>chunk_tokens</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>est_output_tokens</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>citation_pass</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ragas_faithfulness</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ragas_relevancy</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>context_precision</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>context_recall</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pipeline_ms</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>generator_ms</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>total_ms</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>is_recurrent</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>router_ms</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>retrieval_ms</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>generator_node_ms</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>anchor_ms</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>eval_search_ms</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>schedule_filter_ms</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merge_ms</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>answer_preview</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>human_judgment</t>
         </is>
@@ -917,46 +932,49 @@
       <c r="L2" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="n"/>
+      <c r="M2" t="n">
+        <v>113</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
         <v>7186.8</v>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>7186.8</v>
       </c>
-      <c r="V2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>5104.4</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="Y2" s="2" t="n">
         <v>1250.8</v>
       </c>
-      <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="n"/>
-      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="n"/>
+      <c r="AG2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1003,46 +1021,49 @@
       <c r="L3" s="2" t="n">
         <v>573</v>
       </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n"/>
+      <c r="M3" t="n">
+        <v>450</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
         <v>5428.9</v>
       </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>5428.9</v>
       </c>
-      <c r="V3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="n">
         <v>4545.5</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="Y3" s="2" t="n">
         <v>573.2</v>
       </c>
-      <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
       <c r="AA3" s="2" t="n"/>
       <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="n"/>
-      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="n"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="n"/>
+      <c r="AG3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1085,46 +1106,49 @@
       <c r="L4" s="2" t="n">
         <v>1402</v>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n"/>
+      <c r="M4" t="n">
+        <v>1331</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n">
         <v>0.5833</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.6667</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>6337.6</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>6337.6</v>
       </c>
-      <c r="V4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>3810.4</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="Y4" s="2" t="n">
         <v>2209.9</v>
       </c>
-      <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="n"/>
       <c r="AC4" s="2" t="n"/>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="n"/>
+      <c r="AG4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1167,46 +1191,49 @@
       <c r="L5" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n"/>
+      <c r="M5" t="n">
+        <v>155</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>3511.7</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
         <v>3511.7</v>
       </c>
-      <c r="V5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2" t="n">
         <v>2828.7</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="Y5" s="2" t="n">
         <v>515.8</v>
       </c>
-      <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="n"/>
       <c r="AA5" s="2" t="n"/>
       <c r="AB5" s="2" t="n"/>
       <c r="AC5" s="2" t="n"/>
-      <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="n"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="n"/>
+      <c r="AG5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1253,46 +1280,49 @@
       <c r="L6" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n"/>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>5110.8</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>5110.8</v>
       </c>
-      <c r="V6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="n">
         <v>3923.5</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="Y6" s="2" t="n">
         <v>1008.4</v>
       </c>
-      <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="2" t="n"/>
       <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="n"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="n"/>
+      <c r="AG6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1339,46 +1369,49 @@
       <c r="L7" s="2" t="n">
         <v>596</v>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n"/>
+      <c r="M7" t="n">
+        <v>567</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>4253.7</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
         <v>4253.7</v>
       </c>
-      <c r="V7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>2792</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="Y7" s="2" t="n">
         <v>1262.7</v>
       </c>
-      <c r="Y7" s="2" t="n"/>
       <c r="Z7" s="2" t="n"/>
       <c r="AA7" s="2" t="n"/>
       <c r="AB7" s="2" t="n"/>
       <c r="AC7" s="2" t="n"/>
-      <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="n"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="n"/>
+      <c r="AG7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1425,46 +1458,49 @@
       <c r="L8" s="2" t="n">
         <v>562</v>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n"/>
+      <c r="M8" t="n">
+        <v>497</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
         <v>6955.2</v>
       </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
         <v>6955.2</v>
       </c>
-      <c r="V8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2" t="n">
+      <c r="W8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="n">
         <v>4337</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="Y8" s="2" t="n">
         <v>2408</v>
       </c>
-      <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
       <c r="AA8" s="2" t="n"/>
       <c r="AB8" s="2" t="n"/>
       <c r="AC8" s="2" t="n"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="n"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="n"/>
+      <c r="AG8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1507,46 +1543,49 @@
       <c r="L9" s="2" t="n">
         <v>1427</v>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n"/>
+      <c r="M9" t="n">
+        <v>1387</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
         <v>4398.6</v>
       </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
         <v>4398.6</v>
       </c>
-      <c r="V9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2" t="n">
+      <c r="W9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2" t="n">
         <v>2497.8</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="Y9" s="2" t="n">
         <v>1681.5</v>
       </c>
-      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="n"/>
       <c r="AA9" s="2" t="n"/>
       <c r="AB9" s="2" t="n"/>
       <c r="AC9" s="2" t="n"/>
-      <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="n"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="n"/>
+      <c r="AG9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1589,46 +1628,49 @@
       <c r="L10" s="2" t="n">
         <v>1529</v>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n"/>
+      <c r="M10" t="n">
+        <v>1511</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="n">
         <v>4984</v>
       </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>4984</v>
       </c>
-      <c r="V10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="2" t="n">
+      <c r="W10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2" t="n">
         <v>2890.7</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="Y10" s="2" t="n">
         <v>1877.1</v>
       </c>
-      <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n"/>
       <c r="AC10" s="2" t="n"/>
-      <c r="AD10" s="2" t="inlineStr"/>
-      <c r="AE10" s="2" t="n"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="n"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="n"/>
+      <c r="AG10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1671,46 +1713,49 @@
       <c r="L11" s="2" t="n">
         <v>1369</v>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n"/>
+      <c r="M11" t="n">
+        <v>1320</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2" t="n">
         <v>5171.1</v>
       </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>5171.1</v>
       </c>
-      <c r="V11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2" t="n">
         <v>3017</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="Y11" s="2" t="n">
         <v>1918.2</v>
       </c>
-      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" s="2" t="n"/>
       <c r="AB11" s="2" t="n"/>
       <c r="AC11" s="2" t="n"/>
-      <c r="AD11" s="2" t="inlineStr"/>
-      <c r="AE11" s="2" t="n"/>
-      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="n"/>
+      <c r="AG11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1753,46 +1798,49 @@
       <c r="L12" s="2" t="n">
         <v>1560</v>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n"/>
+      <c r="M12" t="n">
+        <v>1462</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n">
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n">
         <v>0.6389</v>
       </c>
-      <c r="R12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="n">
         <v>4718.9</v>
       </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="n">
         <v>4718.9</v>
       </c>
-      <c r="V12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" s="2" t="n">
+      <c r="W12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2" t="n">
         <v>2661.6</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="Y12" s="2" t="n">
         <v>1848.3</v>
       </c>
-      <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="n"/>
       <c r="AA12" s="2" t="n"/>
       <c r="AB12" s="2" t="n"/>
       <c r="AC12" s="2" t="n"/>
-      <c r="AD12" s="2" t="inlineStr"/>
-      <c r="AE12" s="2" t="n"/>
-      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="n"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="n"/>
+      <c r="AG12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1835,46 +1883,49 @@
       <c r="L13" s="2" t="n">
         <v>1071</v>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n"/>
+      <c r="M13" t="n">
+        <v>1058</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
         <v>13642.9</v>
       </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
         <v>13642.9</v>
       </c>
-      <c r="V13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2" t="n">
+      <c r="W13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="n">
         <v>12637.6</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="Y13" s="2" t="n">
         <v>809.4</v>
       </c>
-      <c r="Y13" s="2" t="n"/>
       <c r="Z13" s="2" t="n"/>
       <c r="AA13" s="2" t="n"/>
       <c r="AB13" s="2" t="n"/>
       <c r="AC13" s="2" t="n"/>
-      <c r="AD13" s="2" t="inlineStr"/>
-      <c r="AE13" s="2" t="n"/>
-      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="n"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="n"/>
+      <c r="AG13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1917,46 +1968,49 @@
       <c r="L14" s="2" t="n">
         <v>1044</v>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n"/>
+      <c r="M14" t="n">
+        <v>999</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="S14" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="T14" s="2" t="n">
         <v>5505.8</v>
       </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
         <v>5505.8</v>
       </c>
-      <c r="V14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2" t="n">
+      <c r="W14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2" t="n">
         <v>3530.6</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="Y14" s="2" t="n">
         <v>1775.8</v>
       </c>
-      <c r="Y14" s="2" t="n"/>
       <c r="Z14" s="2" t="n"/>
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="n"/>
       <c r="AC14" s="2" t="n"/>
-      <c r="AD14" s="2" t="inlineStr"/>
-      <c r="AE14" s="2" t="n"/>
-      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="n"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="n"/>
+      <c r="AG14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1999,46 +2053,49 @@
       <c r="L15" s="2" t="n">
         <v>1960</v>
       </c>
-      <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n"/>
+      <c r="M15" t="n">
+        <v>1937</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n">
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="R15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="2" t="n">
         <v>5053.2</v>
       </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
         <v>5053.2</v>
       </c>
-      <c r="V15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2" t="n">
         <v>2713.7</v>
       </c>
-      <c r="X15" s="2" t="n">
+      <c r="Y15" s="2" t="n">
         <v>2147.7</v>
       </c>
-      <c r="Y15" s="2" t="n"/>
       <c r="Z15" s="2" t="n"/>
       <c r="AA15" s="2" t="n"/>
       <c r="AB15" s="2" t="n"/>
       <c r="AC15" s="2" t="n"/>
-      <c r="AD15" s="2" t="inlineStr"/>
-      <c r="AE15" s="2" t="n"/>
-      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="n"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="n"/>
+      <c r="AG15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2081,46 +2138,49 @@
       <c r="L16" s="2" t="n">
         <v>501</v>
       </c>
-      <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2" t="n"/>
+      <c r="M16" t="n">
+        <v>451</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q16" s="2" t="n"/>
       <c r="R16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
         <v>6313.6</v>
       </c>
-      <c r="T16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n">
         <v>6313.6</v>
       </c>
-      <c r="V16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2" t="n">
+      <c r="W16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2" t="n">
         <v>3223.9</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="Y16" s="2" t="n">
         <v>2850.7</v>
       </c>
-      <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="n"/>
       <c r="AA16" s="2" t="n"/>
       <c r="AB16" s="2" t="n"/>
       <c r="AC16" s="2" t="n"/>
-      <c r="AD16" s="2" t="inlineStr"/>
-      <c r="AE16" s="2" t="n"/>
-      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="n"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="n"/>
+      <c r="AG16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2167,46 +2227,49 @@
       <c r="L17" s="2" t="n">
         <v>877</v>
       </c>
-      <c r="M17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="2" t="n"/>
+      <c r="M17" t="n">
+        <v>782</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n">
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="R17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="S17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2" t="n">
         <v>5832.5</v>
       </c>
-      <c r="T17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n">
         <v>5832.5</v>
       </c>
-      <c r="V17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2" t="n">
+      <c r="W17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2" t="n">
         <v>3716</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="Y17" s="2" t="n">
         <v>1902.9</v>
       </c>
-      <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
       <c r="AA17" s="2" t="n"/>
       <c r="AB17" s="2" t="n"/>
       <c r="AC17" s="2" t="n"/>
-      <c r="AD17" s="2" t="inlineStr"/>
-      <c r="AE17" s="2" t="n"/>
-      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="n"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="n"/>
+      <c r="AG17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2249,46 +2312,49 @@
       <c r="L18" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="M18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="n"/>
+      <c r="M18" t="n">
+        <v>116</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="2" t="n">
         <v>7269.2</v>
       </c>
-      <c r="T18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="n">
         <v>7269.2</v>
       </c>
-      <c r="V18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2" t="n">
+      <c r="W18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2" t="n">
         <v>4046.8</v>
       </c>
-      <c r="X18" s="2" t="n">
+      <c r="Y18" s="2" t="n">
         <v>3040.7</v>
       </c>
-      <c r="Y18" s="2" t="n"/>
       <c r="Z18" s="2" t="n"/>
       <c r="AA18" s="2" t="n"/>
       <c r="AB18" s="2" t="n"/>
       <c r="AC18" s="2" t="n"/>
-      <c r="AD18" s="2" t="inlineStr"/>
-      <c r="AE18" s="2" t="n"/>
-      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="n"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="n"/>
+      <c r="AG18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2331,46 +2397,49 @@
       <c r="L19" s="2" t="n">
         <v>1840</v>
       </c>
-      <c r="M19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="n"/>
+      <c r="M19" t="n">
+        <v>1799</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n">
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>5521.1</v>
       </c>
-      <c r="T19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="n">
         <v>5521.1</v>
       </c>
-      <c r="V19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W19" s="2" t="n">
+      <c r="W19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2" t="n">
         <v>3111.6</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="Y19" s="2" t="n">
         <v>2228.2</v>
       </c>
-      <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
       <c r="AA19" s="2" t="n"/>
       <c r="AB19" s="2" t="n"/>
       <c r="AC19" s="2" t="n"/>
-      <c r="AD19" s="2" t="inlineStr"/>
-      <c r="AE19" s="2" t="n"/>
-      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="n"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="n"/>
+      <c r="AG19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2413,46 +2482,49 @@
       <c r="L20" s="2" t="n">
         <v>1680</v>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2" t="n"/>
+      <c r="M20" t="n">
+        <v>1664</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n">
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n">
         <v>0.2111</v>
       </c>
-      <c r="R20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
         <v>3940.5</v>
       </c>
-      <c r="T20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="n">
         <v>3940.5</v>
       </c>
-      <c r="V20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2" t="n">
+      <c r="W20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2" t="n">
         <v>2157.8</v>
       </c>
-      <c r="X20" s="2" t="n">
+      <c r="Y20" s="2" t="n">
         <v>1590.2</v>
       </c>
-      <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="n"/>
       <c r="AA20" s="2" t="n"/>
       <c r="AB20" s="2" t="n"/>
       <c r="AC20" s="2" t="n"/>
-      <c r="AD20" s="2" t="inlineStr"/>
-      <c r="AE20" s="2" t="n"/>
-      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="n"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="n"/>
+      <c r="AG20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2495,49 +2567,52 @@
       <c r="L21" s="2" t="n">
         <v>4152</v>
       </c>
-      <c r="M21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2" t="n"/>
+      <c r="M21" t="n">
+        <v>4055</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
         <v>5839.1</v>
       </c>
-      <c r="T21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="n">
         <v>5839.1</v>
       </c>
-      <c r="V21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2" t="n">
+      <c r="W21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2" t="n">
         <v>3362.7</v>
       </c>
-      <c r="X21" s="2" t="n">
+      <c r="Y21" s="2" t="n">
         <v>2247.6</v>
       </c>
-      <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
       <c r="AA21" s="2" t="n"/>
       <c r="AB21" s="2" t="n"/>
       <c r="AC21" s="2" t="n"/>
-      <c r="AD21" s="2" t="inlineStr"/>
-      <c r="AE21" s="2" t="n"/>
-      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="n"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="n"/>
+      <c r="AG21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF21"/>
+  <autoFilter ref="A1:AG21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3034,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3569,6 +3644,23 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>chunk_tokens</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Backfilled: estimated tokens in retrieved chunk content only (no query). Computed as est_input_tokens - len(question)//4. Approximation only — the run-time formula floors the combined sum, which can differ from subtracting floored components by at most 1.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
